--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA564"/>
+  <dimension ref="A1:AA570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -58076,6 +58076,648 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr"/>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="inlineStr"/>
+      <c r="K565" s="2" t="inlineStr"/>
+      <c r="L565" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M565" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N565" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O565" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P565" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q565" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U565" s="2" t="inlineStr"/>
+      <c r="V565" s="2" t="inlineStr"/>
+      <c r="W565" s="2" t="inlineStr">
+        <is>
+          <t>Betsy Haynes</t>
+        </is>
+      </c>
+      <c r="X565" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y565" s="2" t="inlineStr"/>
+      <c r="Z565" s="2" t="inlineStr"/>
+      <c r="AA565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/betsy-haynes-9314a921/</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr"/>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr"/>
+      <c r="L566" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M566" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N566" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O566" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P566" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q566" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U566" s="2" t="inlineStr"/>
+      <c r="V566" s="2" t="inlineStr"/>
+      <c r="W566" s="2" t="inlineStr">
+        <is>
+          <t>Braedon Links</t>
+        </is>
+      </c>
+      <c r="X566" s="2" t="inlineStr">
+        <is>
+          <t>Division Manager - Wine</t>
+        </is>
+      </c>
+      <c r="Y566" s="2" t="inlineStr"/>
+      <c r="Z566" s="2" t="inlineStr"/>
+      <c r="AA566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/braedonlinks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr"/>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="inlineStr"/>
+      <c r="K567" s="2" t="inlineStr"/>
+      <c r="L567" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M567" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N567" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O567" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P567" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q567" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U567" s="2" t="inlineStr"/>
+      <c r="V567" s="2" t="inlineStr"/>
+      <c r="W567" s="2" t="inlineStr">
+        <is>
+          <t>Louie Alcaraz</t>
+        </is>
+      </c>
+      <c r="X567" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y567" s="2" t="inlineStr"/>
+      <c r="Z567" s="2" t="inlineStr"/>
+      <c r="AA567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louiealcaraz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr"/>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr"/>
+      <c r="L568" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N568" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O568" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P568" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q568" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U568" s="2" t="inlineStr"/>
+      <c r="V568" s="2" t="inlineStr"/>
+      <c r="W568" s="2" t="inlineStr">
+        <is>
+          <t>Jesyca Wan</t>
+        </is>
+      </c>
+      <c r="X568" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y568" s="2" t="inlineStr"/>
+      <c r="Z568" s="2" t="inlineStr"/>
+      <c r="AA568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jesycawan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr"/>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="inlineStr"/>
+      <c r="K569" s="2" t="inlineStr"/>
+      <c r="L569" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N569" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O569" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P569" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q569" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U569" s="2" t="inlineStr"/>
+      <c r="V569" s="2" t="inlineStr"/>
+      <c r="W569" s="2" t="inlineStr">
+        <is>
+          <t>Dennis Cheung</t>
+        </is>
+      </c>
+      <c r="X569" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y569" s="2" t="inlineStr"/>
+      <c r="Z569" s="2" t="inlineStr"/>
+      <c r="AA569" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/dennis-cheung-a2175714a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>32596</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>Kabo Commercial Building, 18-20 Pai Fa Street</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr"/>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chillax.hk</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr"/>
+      <c r="L570" s="2" t="inlineStr"/>
+      <c r="M570" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N570" s="2" t="inlineStr">
+        <is>
+          <t>edward.hung@chillax.hk</t>
+        </is>
+      </c>
+      <c r="O570" s="2" t="inlineStr"/>
+      <c r="P570" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q570" s="2" t="inlineStr"/>
+      <c r="R570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chillax-international-limited/</t>
+        </is>
+      </c>
+      <c r="S570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="T570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="U570" s="2" t="inlineStr"/>
+      <c r="V570" s="2" t="inlineStr"/>
+      <c r="W570" s="2" t="inlineStr">
+        <is>
+          <t>Edward Hung</t>
+        </is>
+      </c>
+      <c r="X570" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y570" s="2" t="inlineStr"/>
+      <c r="Z570" s="2" t="inlineStr"/>
+      <c r="AA570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edward-hung/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA570"/>
+  <dimension ref="A1:AA576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -58718,6 +58718,648 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr"/>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J571" s="2" t="inlineStr"/>
+      <c r="K571" s="2" t="inlineStr"/>
+      <c r="L571" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M571" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N571" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O571" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P571" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q571" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U571" s="2" t="inlineStr"/>
+      <c r="V571" s="2" t="inlineStr"/>
+      <c r="W571" s="2" t="inlineStr">
+        <is>
+          <t>Betsy Haynes</t>
+        </is>
+      </c>
+      <c r="X571" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y571" s="2" t="inlineStr"/>
+      <c r="Z571" s="2" t="inlineStr"/>
+      <c r="AA571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/betsy-haynes-9314a921/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr"/>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr"/>
+      <c r="L572" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M572" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N572" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O572" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P572" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q572" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U572" s="2" t="inlineStr"/>
+      <c r="V572" s="2" t="inlineStr"/>
+      <c r="W572" s="2" t="inlineStr">
+        <is>
+          <t>Braedon Links</t>
+        </is>
+      </c>
+      <c r="X572" s="2" t="inlineStr">
+        <is>
+          <t>Division Manager - Wine</t>
+        </is>
+      </c>
+      <c r="Y572" s="2" t="inlineStr"/>
+      <c r="Z572" s="2" t="inlineStr"/>
+      <c r="AA572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/braedonlinks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr"/>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J573" s="2" t="inlineStr"/>
+      <c r="K573" s="2" t="inlineStr"/>
+      <c r="L573" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M573" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N573" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O573" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P573" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q573" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U573" s="2" t="inlineStr"/>
+      <c r="V573" s="2" t="inlineStr"/>
+      <c r="W573" s="2" t="inlineStr">
+        <is>
+          <t>Jesyca Wan</t>
+        </is>
+      </c>
+      <c r="X573" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y573" s="2" t="inlineStr"/>
+      <c r="Z573" s="2" t="inlineStr"/>
+      <c r="AA573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jesycawan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr"/>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="inlineStr"/>
+      <c r="K574" s="2" t="inlineStr"/>
+      <c r="L574" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M574" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N574" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O574" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P574" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q574" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U574" s="2" t="inlineStr"/>
+      <c r="V574" s="2" t="inlineStr"/>
+      <c r="W574" s="2" t="inlineStr">
+        <is>
+          <t>Louie Alcaraz</t>
+        </is>
+      </c>
+      <c r="X574" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y574" s="2" t="inlineStr"/>
+      <c r="Z574" s="2" t="inlineStr"/>
+      <c r="AA574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louiealcaraz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr"/>
+      <c r="I575" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="inlineStr"/>
+      <c r="K575" s="2" t="inlineStr"/>
+      <c r="L575" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M575" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N575" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O575" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P575" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q575" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U575" s="2" t="inlineStr"/>
+      <c r="V575" s="2" t="inlineStr"/>
+      <c r="W575" s="2" t="inlineStr">
+        <is>
+          <t>Dennis Cheung</t>
+        </is>
+      </c>
+      <c r="X575" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y575" s="2" t="inlineStr"/>
+      <c r="Z575" s="2" t="inlineStr"/>
+      <c r="AA575" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/dennis-cheung-a2175714a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>32596</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>Kabo Commercial Building, 18-20 Pai Fa Street</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr"/>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chillax.hk</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr"/>
+      <c r="K576" s="2" t="inlineStr"/>
+      <c r="L576" s="2" t="inlineStr"/>
+      <c r="M576" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N576" s="2" t="inlineStr">
+        <is>
+          <t>edward.hung@chillax.hk</t>
+        </is>
+      </c>
+      <c r="O576" s="2" t="inlineStr"/>
+      <c r="P576" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q576" s="2" t="inlineStr"/>
+      <c r="R576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chillax-international-limited/</t>
+        </is>
+      </c>
+      <c r="S576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="T576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="U576" s="2" t="inlineStr"/>
+      <c r="V576" s="2" t="inlineStr"/>
+      <c r="W576" s="2" t="inlineStr">
+        <is>
+          <t>Edward Hung</t>
+        </is>
+      </c>
+      <c r="X576" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y576" s="2" t="inlineStr"/>
+      <c r="Z576" s="2" t="inlineStr"/>
+      <c r="AA576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edward-hung/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA576"/>
+  <dimension ref="A1:AA583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -59360,6 +59360,753 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Ping Shan Enterprise Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>Ping Shan Enterprise Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>7676</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>Seaview Commercial Building, 21-24 Connaught Road West, Sheung Wan</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr"/>
+      <c r="I577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.psf.com.hk</t>
+        </is>
+      </c>
+      <c r="J577" s="2" t="inlineStr"/>
+      <c r="K577" s="2" t="inlineStr"/>
+      <c r="L577" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M577" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N577" s="2" t="inlineStr">
+        <is>
+          <t>Jack@pingshan.com.hk</t>
+        </is>
+      </c>
+      <c r="O577" s="2" t="inlineStr">
+        <is>
+          <t>+852 2858 1188</t>
+        </is>
+      </c>
+      <c r="P577" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="Q577" s="2" t="inlineStr">
+        <is>
+          <t>01936787-000</t>
+        </is>
+      </c>
+      <c r="R577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ping-shan-enterprise-co-ltd/</t>
+        </is>
+      </c>
+      <c r="S577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pingshanfoods.hk/</t>
+        </is>
+      </c>
+      <c r="T577" s="2" t="inlineStr"/>
+      <c r="U577" s="2" t="inlineStr"/>
+      <c r="V577" s="2" t="inlineStr"/>
+      <c r="W577" s="2" t="inlineStr">
+        <is>
+          <t>Jack Lee</t>
+        </is>
+      </c>
+      <c r="X577" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y577" s="2" t="inlineStr"/>
+      <c r="Z577" s="2" t="inlineStr"/>
+      <c r="AA577" s="2" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/in/jack-lee-322b6b62</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr"/>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr"/>
+      <c r="K578" s="2" t="inlineStr"/>
+      <c r="L578" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M578" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N578" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O578" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P578" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q578" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U578" s="2" t="inlineStr"/>
+      <c r="V578" s="2" t="inlineStr"/>
+      <c r="W578" s="2" t="inlineStr">
+        <is>
+          <t>Betsy Haynes</t>
+        </is>
+      </c>
+      <c r="X578" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y578" s="2" t="inlineStr"/>
+      <c r="Z578" s="2" t="inlineStr"/>
+      <c r="AA578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/betsy-haynes-9314a921/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr"/>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="inlineStr"/>
+      <c r="K579" s="2" t="inlineStr"/>
+      <c r="L579" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M579" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N579" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O579" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P579" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q579" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U579" s="2" t="inlineStr"/>
+      <c r="V579" s="2" t="inlineStr"/>
+      <c r="W579" s="2" t="inlineStr">
+        <is>
+          <t>Braedon Links</t>
+        </is>
+      </c>
+      <c r="X579" s="2" t="inlineStr">
+        <is>
+          <t>Division Manager - Wine</t>
+        </is>
+      </c>
+      <c r="Y579" s="2" t="inlineStr"/>
+      <c r="Z579" s="2" t="inlineStr"/>
+      <c r="AA579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/braedonlinks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr"/>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr"/>
+      <c r="L580" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M580" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N580" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O580" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P580" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q580" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U580" s="2" t="inlineStr"/>
+      <c r="V580" s="2" t="inlineStr"/>
+      <c r="W580" s="2" t="inlineStr">
+        <is>
+          <t>Jesyca Wan</t>
+        </is>
+      </c>
+      <c r="X580" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y580" s="2" t="inlineStr"/>
+      <c r="Z580" s="2" t="inlineStr"/>
+      <c r="AA580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jesycawan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr"/>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="inlineStr"/>
+      <c r="K581" s="2" t="inlineStr"/>
+      <c r="L581" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M581" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N581" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O581" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P581" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q581" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U581" s="2" t="inlineStr"/>
+      <c r="V581" s="2" t="inlineStr"/>
+      <c r="W581" s="2" t="inlineStr">
+        <is>
+          <t>Louie Alcaraz</t>
+        </is>
+      </c>
+      <c r="X581" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y581" s="2" t="inlineStr"/>
+      <c r="Z581" s="2" t="inlineStr"/>
+      <c r="AA581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louiealcaraz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr"/>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr"/>
+      <c r="L582" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M582" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N582" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O582" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P582" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q582" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U582" s="2" t="inlineStr"/>
+      <c r="V582" s="2" t="inlineStr"/>
+      <c r="W582" s="2" t="inlineStr">
+        <is>
+          <t>Dennis Cheung</t>
+        </is>
+      </c>
+      <c r="X582" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y582" s="2" t="inlineStr"/>
+      <c r="Z582" s="2" t="inlineStr"/>
+      <c r="AA582" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/dennis-cheung-a2175714a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>32596</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>Kabo Commercial Building, 18-20 Pai Fa Street</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr"/>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chillax.hk</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="inlineStr"/>
+      <c r="K583" s="2" t="inlineStr"/>
+      <c r="L583" s="2" t="inlineStr"/>
+      <c r="M583" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N583" s="2" t="inlineStr">
+        <is>
+          <t>edward.hung@chillax.hk</t>
+        </is>
+      </c>
+      <c r="O583" s="2" t="inlineStr"/>
+      <c r="P583" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q583" s="2" t="inlineStr"/>
+      <c r="R583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chillax-international-limited/</t>
+        </is>
+      </c>
+      <c r="S583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="T583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="U583" s="2" t="inlineStr"/>
+      <c r="V583" s="2" t="inlineStr"/>
+      <c r="W583" s="2" t="inlineStr">
+        <is>
+          <t>Edward Hung</t>
+        </is>
+      </c>
+      <c r="X583" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y583" s="2" t="inlineStr"/>
+      <c r="Z583" s="2" t="inlineStr"/>
+      <c r="AA583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edward-hung/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA583"/>
+  <dimension ref="A1:AA594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -60107,6 +60107,1129 @@
         </is>
       </c>
     </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>Cws Fine Wines</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>Cws Fine Wines</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>47967</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>Olympia Plaza, 255 King's Road, North Point</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr"/>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>https://cellar-door.wine</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr"/>
+      <c r="K584" s="2" t="inlineStr"/>
+      <c r="L584" s="2" t="inlineStr"/>
+      <c r="M584" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N584" s="2" t="inlineStr">
+        <is>
+          <t>info@cws.wine</t>
+        </is>
+      </c>
+      <c r="O584" s="2" t="inlineStr">
+        <is>
+          <t>+852 3611 6476</t>
+        </is>
+      </c>
+      <c r="P584" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q584" s="2" t="inlineStr"/>
+      <c r="R584" s="2" t="inlineStr"/>
+      <c r="S584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CWSHKG/</t>
+        </is>
+      </c>
+      <c r="T584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cws_finewines/</t>
+        </is>
+      </c>
+      <c r="U584" s="2" t="inlineStr"/>
+      <c r="V584" s="2" t="inlineStr"/>
+      <c r="W584" s="2" t="inlineStr">
+        <is>
+          <t>Wilfried Sentex</t>
+        </is>
+      </c>
+      <c r="X584" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y584" s="2" t="inlineStr"/>
+      <c r="Z584" s="2" t="inlineStr"/>
+      <c r="AA584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wilfried-sentex-22656419/</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Alcohood Limited</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>Alcohood Limited</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>96364</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>Mega Trade Centre, 1 Mei Wan Street,</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr"/>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>https://en.alcohood.com</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="inlineStr"/>
+      <c r="K585" s="2" t="inlineStr"/>
+      <c r="L585" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M585" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N585" s="2" t="inlineStr">
+        <is>
+          <t>info@alcohood.com</t>
+        </is>
+      </c>
+      <c r="O585" s="2" t="inlineStr"/>
+      <c r="P585" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q585" s="2" t="inlineStr">
+        <is>
+          <t>72424234-000</t>
+        </is>
+      </c>
+      <c r="R585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alcohood-ltd/</t>
+        </is>
+      </c>
+      <c r="S585" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/Alcohoodhk</t>
+        </is>
+      </c>
+      <c r="T585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alcohoodhk</t>
+        </is>
+      </c>
+      <c r="U585" s="2" t="inlineStr"/>
+      <c r="V585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCkHcfj3pNJMFeWDYI8cP5AA/</t>
+        </is>
+      </c>
+      <c r="W585" s="2" t="inlineStr">
+        <is>
+          <t>Billy Ng</t>
+        </is>
+      </c>
+      <c r="X585" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y585" s="2" t="inlineStr"/>
+      <c r="Z585" s="2" t="inlineStr"/>
+      <c r="AA585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/billy-ng/</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>Cheers Mate</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>Cheers Mate</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>Kam Ho Court, 144-148 Belcher's Street</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr"/>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cheersmate.hk</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr"/>
+      <c r="L586" s="2" t="inlineStr"/>
+      <c r="M586" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N586" s="2" t="inlineStr">
+        <is>
+          <t>ktownliquor.hk@gmail.com</t>
+        </is>
+      </c>
+      <c r="O586" s="2" t="inlineStr">
+        <is>
+          <t>+852 2838 8200</t>
+        </is>
+      </c>
+      <c r="P586" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q586" s="2" t="inlineStr"/>
+      <c r="R586" s="2" t="inlineStr"/>
+      <c r="S586" s="2" t="inlineStr"/>
+      <c r="T586" s="2" t="inlineStr"/>
+      <c r="U586" s="2" t="inlineStr"/>
+      <c r="V586" s="2" t="inlineStr"/>
+      <c r="W586" s="2" t="inlineStr"/>
+      <c r="X586" s="2" t="inlineStr"/>
+      <c r="Y586" s="2" t="inlineStr"/>
+      <c r="Z586" s="2" t="inlineStr"/>
+      <c r="AA586" s="2" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>Heritage Wines Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>Heritage Wines Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>22024</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>The Sparkle Tower 1, 500 Tung Chau Street</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr"/>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>https://heritagewines.com.hk</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="inlineStr"/>
+      <c r="K587" s="2" t="inlineStr"/>
+      <c r="L587" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M587" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N587" s="2" t="inlineStr">
+        <is>
+          <t>sales@heritagewines.com.hk</t>
+        </is>
+      </c>
+      <c r="O587" s="2" t="inlineStr"/>
+      <c r="P587" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q587" s="2" t="inlineStr">
+        <is>
+          <t>62270398-000</t>
+        </is>
+      </c>
+      <c r="R587" s="2" t="inlineStr"/>
+      <c r="S587" s="2" t="inlineStr"/>
+      <c r="T587" s="2" t="inlineStr"/>
+      <c r="U587" s="2" t="inlineStr"/>
+      <c r="V587" s="2" t="inlineStr"/>
+      <c r="W587" s="2" t="inlineStr">
+        <is>
+          <t>Roberto Cioaca</t>
+        </is>
+      </c>
+      <c r="X587" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Director</t>
+        </is>
+      </c>
+      <c r="Y587" s="2" t="inlineStr"/>
+      <c r="Z587" s="2" t="inlineStr"/>
+      <c r="AA587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roberto-cioaca-83210625</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>Ping Shan Enterprise Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>Ping Shan Enterprise Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>7676</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>Seaview Commercial Building, 21-24 Connaught Road West, Sheung Wan</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr"/>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.psf.com.hk</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr"/>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M588" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N588" s="2" t="inlineStr">
+        <is>
+          <t>Jack@pingshan.com.hk</t>
+        </is>
+      </c>
+      <c r="O588" s="2" t="inlineStr">
+        <is>
+          <t>+852 2858 1188</t>
+        </is>
+      </c>
+      <c r="P588" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="Q588" s="2" t="inlineStr">
+        <is>
+          <t>01936787-000</t>
+        </is>
+      </c>
+      <c r="R588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ping-shan-enterprise-co-ltd/</t>
+        </is>
+      </c>
+      <c r="S588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pingshanfoods.hk/</t>
+        </is>
+      </c>
+      <c r="T588" s="2" t="inlineStr"/>
+      <c r="U588" s="2" t="inlineStr"/>
+      <c r="V588" s="2" t="inlineStr"/>
+      <c r="W588" s="2" t="inlineStr">
+        <is>
+          <t>Jack Lee</t>
+        </is>
+      </c>
+      <c r="X588" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y588" s="2" t="inlineStr"/>
+      <c r="Z588" s="2" t="inlineStr"/>
+      <c r="AA588" s="2" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/in/jack-lee-322b6b62</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr"/>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="inlineStr"/>
+      <c r="K589" s="2" t="inlineStr"/>
+      <c r="L589" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M589" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N589" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O589" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P589" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q589" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U589" s="2" t="inlineStr"/>
+      <c r="V589" s="2" t="inlineStr"/>
+      <c r="W589" s="2" t="inlineStr">
+        <is>
+          <t>Betsy Haynes</t>
+        </is>
+      </c>
+      <c r="X589" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y589" s="2" t="inlineStr"/>
+      <c r="Z589" s="2" t="inlineStr"/>
+      <c r="AA589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/betsy-haynes-9314a921/</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr"/>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr"/>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M590" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N590" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O590" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P590" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q590" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U590" s="2" t="inlineStr"/>
+      <c r="V590" s="2" t="inlineStr"/>
+      <c r="W590" s="2" t="inlineStr">
+        <is>
+          <t>Braedon Links</t>
+        </is>
+      </c>
+      <c r="X590" s="2" t="inlineStr">
+        <is>
+          <t>Division Manager - Wine</t>
+        </is>
+      </c>
+      <c r="Y590" s="2" t="inlineStr"/>
+      <c r="Z590" s="2" t="inlineStr"/>
+      <c r="AA590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/braedonlinks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr"/>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J591" s="2" t="inlineStr"/>
+      <c r="K591" s="2" t="inlineStr"/>
+      <c r="L591" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M591" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N591" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O591" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P591" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q591" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U591" s="2" t="inlineStr"/>
+      <c r="V591" s="2" t="inlineStr"/>
+      <c r="W591" s="2" t="inlineStr">
+        <is>
+          <t>Louie Alcaraz</t>
+        </is>
+      </c>
+      <c r="X591" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y591" s="2" t="inlineStr"/>
+      <c r="Z591" s="2" t="inlineStr"/>
+      <c r="AA591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louiealcaraz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr"/>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J592" s="2" t="inlineStr"/>
+      <c r="K592" s="2" t="inlineStr"/>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M592" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N592" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O592" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P592" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q592" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U592" s="2" t="inlineStr"/>
+      <c r="V592" s="2" t="inlineStr"/>
+      <c r="W592" s="2" t="inlineStr">
+        <is>
+          <t>Jesyca Wan</t>
+        </is>
+      </c>
+      <c r="X592" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y592" s="2" t="inlineStr"/>
+      <c r="Z592" s="2" t="inlineStr"/>
+      <c r="AA592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jesycawan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>Northeast Wines &amp; Spirits Limited</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>29 Wong Chuk Hang Road</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr"/>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>https://northeast.com.hk, https://winenthingshk.com</t>
+        </is>
+      </c>
+      <c r="J593" s="2" t="inlineStr"/>
+      <c r="K593" s="2" t="inlineStr"/>
+      <c r="L593" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M593" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N593" s="2" t="inlineStr">
+        <is>
+          <t>orders@northeast.com.hk</t>
+        </is>
+      </c>
+      <c r="O593" s="2" t="inlineStr">
+        <is>
+          <t>+852 2873 5733</t>
+        </is>
+      </c>
+      <c r="P593" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q593" s="2" t="inlineStr">
+        <is>
+          <t>31354652-000</t>
+        </is>
+      </c>
+      <c r="R593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/northeast-wines-&amp;-spirits-ltd</t>
+        </is>
+      </c>
+      <c r="S593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northeastwineshk/</t>
+        </is>
+      </c>
+      <c r="T593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/northeast_hk/</t>
+        </is>
+      </c>
+      <c r="U593" s="2" t="inlineStr"/>
+      <c r="V593" s="2" t="inlineStr"/>
+      <c r="W593" s="2" t="inlineStr">
+        <is>
+          <t>Dennis Cheung</t>
+        </is>
+      </c>
+      <c r="X593" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y593" s="2" t="inlineStr"/>
+      <c r="Z593" s="2" t="inlineStr"/>
+      <c r="AA593" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/dennis-cheung-a2175714a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>Chillax.hk</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>32596</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>Kabo Commercial Building, 18-20 Pai Fa Street</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr"/>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chillax.hk</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr"/>
+      <c r="L594" s="2" t="inlineStr"/>
+      <c r="M594" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N594" s="2" t="inlineStr">
+        <is>
+          <t>edward.hung@chillax.hk</t>
+        </is>
+      </c>
+      <c r="O594" s="2" t="inlineStr"/>
+      <c r="P594" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q594" s="2" t="inlineStr"/>
+      <c r="R594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chillax-international-limited/</t>
+        </is>
+      </c>
+      <c r="S594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="T594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chillax.hk/</t>
+        </is>
+      </c>
+      <c r="U594" s="2" t="inlineStr"/>
+      <c r="V594" s="2" t="inlineStr"/>
+      <c r="W594" s="2" t="inlineStr">
+        <is>
+          <t>Edward Hung</t>
+        </is>
+      </c>
+      <c r="X594" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y594" s="2" t="inlineStr"/>
+      <c r="Z594" s="2" t="inlineStr"/>
+      <c r="AA594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edward-hung/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA594"/>
+  <dimension ref="A1:AA595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -61230,6 +61230,91 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>T &amp; A Fine Wine Company Limited</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>T&amp;a Fine Wine Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>43026</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>Tsim Sha Tsui</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>Unit B, 15/f, Cameron Plaza, 23-25a, Cameron Road</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr"/>
+      <c r="I595" s="2" t="inlineStr">
+        <is>
+          <t>http://www.tafinewines.com.hk, https://www.tafinewines.com</t>
+        </is>
+      </c>
+      <c r="J595" s="2" t="inlineStr"/>
+      <c r="K595" s="2" t="inlineStr"/>
+      <c r="L595" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M595" s="2" t="inlineStr"/>
+      <c r="N595" s="2" t="inlineStr">
+        <is>
+          <t>info@tafinewines.com.hk</t>
+        </is>
+      </c>
+      <c r="O595" s="2" t="inlineStr"/>
+      <c r="P595" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q595" s="2" t="inlineStr">
+        <is>
+          <t>65068897-000</t>
+        </is>
+      </c>
+      <c r="R595" s="2" t="inlineStr"/>
+      <c r="S595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tafinewinecompany/</t>
+        </is>
+      </c>
+      <c r="T595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/t_a_fine_wines/</t>
+        </is>
+      </c>
+      <c r="U595" s="2" t="inlineStr"/>
+      <c r="V595" s="2" t="inlineStr"/>
+      <c r="W595" s="2" t="inlineStr"/>
+      <c r="X595" s="2" t="inlineStr"/>
+      <c r="Y595" s="2" t="inlineStr"/>
+      <c r="Z595" s="2" t="inlineStr"/>
+      <c r="AA595" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA595"/>
+  <dimension ref="A1:AA598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -61315,6 +61315,285 @@
       <c r="Z595" s="2" t="inlineStr"/>
       <c r="AA595" s="2" t="inlineStr"/>
     </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>90923</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>Trans Asia Centre, 18 Kin Hong Street, Kwai Chung</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>1006-1007</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winpoasia.com</t>
+        </is>
+      </c>
+      <c r="J596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M596" s="2" t="inlineStr"/>
+      <c r="N596" s="2" t="inlineStr">
+        <is>
+          <t>Info@winpoasia.com</t>
+        </is>
+      </c>
+      <c r="O596" s="2" t="inlineStr">
+        <is>
+          <t>+852 2423 8863</t>
+        </is>
+      </c>
+      <c r="P596" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q596" s="2" t="inlineStr">
+        <is>
+          <t>36759011-000</t>
+        </is>
+      </c>
+      <c r="R596" s="2" t="inlineStr"/>
+      <c r="S596" s="2" t="inlineStr"/>
+      <c r="T596" s="2" t="inlineStr"/>
+      <c r="U596" s="2" t="inlineStr"/>
+      <c r="V596" s="2" t="inlineStr"/>
+      <c r="W596" s="2" t="inlineStr"/>
+      <c r="X596" s="2" t="inlineStr"/>
+      <c r="Y596" s="2" t="inlineStr"/>
+      <c r="Z596" s="2" t="inlineStr"/>
+      <c r="AA596" s="2" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr"/>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J597" s="2" t="inlineStr"/>
+      <c r="K597" s="2" t="inlineStr"/>
+      <c r="L597" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M597" s="2" t="inlineStr"/>
+      <c r="N597" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O597" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P597" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q597" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R597" s="2" t="inlineStr"/>
+      <c r="S597" s="2" t="inlineStr"/>
+      <c r="T597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U597" s="2" t="inlineStr"/>
+      <c r="V597" s="2" t="inlineStr"/>
+      <c r="W597" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Cheung</t>
+        </is>
+      </c>
+      <c r="X597" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y597" s="2" t="inlineStr"/>
+      <c r="Z597" s="2" t="inlineStr"/>
+      <c r="AA597" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/ronald-cheung-44568278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr"/>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr"/>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M598" s="2" t="inlineStr"/>
+      <c r="N598" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O598" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P598" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q598" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R598" s="2" t="inlineStr"/>
+      <c r="S598" s="2" t="inlineStr"/>
+      <c r="T598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U598" s="2" t="inlineStr"/>
+      <c r="V598" s="2" t="inlineStr"/>
+      <c r="W598" s="2" t="inlineStr">
+        <is>
+          <t>Franky Hong</t>
+        </is>
+      </c>
+      <c r="X598" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y598" s="2" t="inlineStr"/>
+      <c r="Z598" s="2" t="inlineStr"/>
+      <c r="AA598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franky-hong-0a0a53aa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA598"/>
+  <dimension ref="A1:AA603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -61594,6 +61594,443 @@
         </is>
       </c>
     </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>122274</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>Jing Ho Industrial Building, 78-84 Wang Lung Street</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr"/>
+      <c r="I599" s="2" t="inlineStr">
+        <is>
+          <t>https://apus.us</t>
+        </is>
+      </c>
+      <c r="J599" s="2" t="inlineStr"/>
+      <c r="K599" s="2" t="inlineStr"/>
+      <c r="L599" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M599" s="2" t="inlineStr"/>
+      <c r="N599" s="2" t="inlineStr">
+        <is>
+          <t>info@apus.us</t>
+        </is>
+      </c>
+      <c r="O599" s="2" t="inlineStr">
+        <is>
+          <t>+852 3525 0550</t>
+        </is>
+      </c>
+      <c r="P599" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q599" s="2" t="inlineStr">
+        <is>
+          <t>14006171-000</t>
+        </is>
+      </c>
+      <c r="R599" s="2" t="inlineStr"/>
+      <c r="S599" s="2" t="inlineStr"/>
+      <c r="T599" s="2" t="inlineStr"/>
+      <c r="U599" s="2" t="inlineStr"/>
+      <c r="V599" s="2" t="inlineStr"/>
+      <c r="W599" s="2" t="inlineStr"/>
+      <c r="X599" s="2" t="inlineStr"/>
+      <c r="Y599" s="2" t="inlineStr"/>
+      <c r="Z599" s="2" t="inlineStr"/>
+      <c r="AA599" s="2" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>24981</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>317-319 Des Voeux Road Central</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr"/>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="inlineStr"/>
+      <c r="K600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M600" s="2" t="inlineStr"/>
+      <c r="N600" s="2" t="inlineStr">
+        <is>
+          <t>sales@asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="O600" s="2" t="inlineStr"/>
+      <c r="P600" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q600" s="2" t="inlineStr">
+        <is>
+          <t>74431249-000</t>
+        </is>
+      </c>
+      <c r="R600" s="2" t="inlineStr"/>
+      <c r="S600" s="2" t="inlineStr"/>
+      <c r="T600" s="2" t="inlineStr"/>
+      <c r="U600" s="2" t="inlineStr"/>
+      <c r="V600" s="2" t="inlineStr"/>
+      <c r="W600" s="2" t="inlineStr"/>
+      <c r="X600" s="2" t="inlineStr"/>
+      <c r="Y600" s="2" t="inlineStr"/>
+      <c r="Z600" s="2" t="inlineStr"/>
+      <c r="AA600" s="2" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>90923</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>Trans Asia Centre, 18 Kin Hong Street, Kwai Chung</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>1006-1007</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winpoasia.com</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="inlineStr"/>
+      <c r="K601" s="2" t="inlineStr"/>
+      <c r="L601" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M601" s="2" t="inlineStr"/>
+      <c r="N601" s="2" t="inlineStr">
+        <is>
+          <t>Info@winpoasia.com</t>
+        </is>
+      </c>
+      <c r="O601" s="2" t="inlineStr">
+        <is>
+          <t>+852 2423 8863</t>
+        </is>
+      </c>
+      <c r="P601" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q601" s="2" t="inlineStr">
+        <is>
+          <t>36759011-000</t>
+        </is>
+      </c>
+      <c r="R601" s="2" t="inlineStr"/>
+      <c r="S601" s="2" t="inlineStr"/>
+      <c r="T601" s="2" t="inlineStr"/>
+      <c r="U601" s="2" t="inlineStr"/>
+      <c r="V601" s="2" t="inlineStr"/>
+      <c r="W601" s="2" t="inlineStr"/>
+      <c r="X601" s="2" t="inlineStr"/>
+      <c r="Y601" s="2" t="inlineStr"/>
+      <c r="Z601" s="2" t="inlineStr"/>
+      <c r="AA601" s="2" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr"/>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr"/>
+      <c r="K602" s="2" t="inlineStr"/>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M602" s="2" t="inlineStr"/>
+      <c r="N602" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O602" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P602" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q602" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R602" s="2" t="inlineStr"/>
+      <c r="S602" s="2" t="inlineStr"/>
+      <c r="T602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U602" s="2" t="inlineStr"/>
+      <c r="V602" s="2" t="inlineStr"/>
+      <c r="W602" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Cheung</t>
+        </is>
+      </c>
+      <c r="X602" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y602" s="2" t="inlineStr"/>
+      <c r="Z602" s="2" t="inlineStr"/>
+      <c r="AA602" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/ronald-cheung-44568278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr"/>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="inlineStr"/>
+      <c r="K603" s="2" t="inlineStr"/>
+      <c r="L603" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M603" s="2" t="inlineStr"/>
+      <c r="N603" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O603" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P603" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q603" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R603" s="2" t="inlineStr"/>
+      <c r="S603" s="2" t="inlineStr"/>
+      <c r="T603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U603" s="2" t="inlineStr"/>
+      <c r="V603" s="2" t="inlineStr"/>
+      <c r="W603" s="2" t="inlineStr">
+        <is>
+          <t>Franky Hong</t>
+        </is>
+      </c>
+      <c r="X603" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y603" s="2" t="inlineStr"/>
+      <c r="Z603" s="2" t="inlineStr"/>
+      <c r="AA603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franky-hong-0a0a53aa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA603"/>
+  <dimension ref="A1:AA611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -62031,6 +62031,738 @@
         </is>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Wine Guru Company Limited</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>Wine Guru Company Limited</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>117186</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>33-35 Yip Kan Street, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr"/>
+      <c r="I604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineguru.com.hk, https://www.wineguruwines.com</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="inlineStr"/>
+      <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M604" s="2" t="inlineStr"/>
+      <c r="N604" s="2" t="inlineStr">
+        <is>
+          <t>sales@wineguru.com.hk</t>
+        </is>
+      </c>
+      <c r="O604" s="2" t="inlineStr"/>
+      <c r="P604" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q604" s="2" t="inlineStr">
+        <is>
+          <t>60345218-000</t>
+        </is>
+      </c>
+      <c r="R604" s="2" t="inlineStr"/>
+      <c r="S604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineguruhk</t>
+        </is>
+      </c>
+      <c r="T604" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/wineguruhk</t>
+        </is>
+      </c>
+      <c r="U604" s="2" t="inlineStr"/>
+      <c r="V604" s="2" t="inlineStr"/>
+      <c r="W604" s="2" t="inlineStr"/>
+      <c r="X604" s="2" t="inlineStr"/>
+      <c r="Y604" s="2" t="inlineStr"/>
+      <c r="Z604" s="2" t="inlineStr"/>
+      <c r="AA604" s="2" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>Units F&amp;g, 18/f Golden Sun Centre  59-67 Bonham Strand West</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr"/>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>https://winepleasehk.com, https://www.kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="inlineStr"/>
+      <c r="K605" s="2" t="inlineStr"/>
+      <c r="L605" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M605" s="2" t="inlineStr"/>
+      <c r="N605" s="2" t="inlineStr">
+        <is>
+          <t>info@kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="O605" s="2" t="inlineStr">
+        <is>
+          <t>+852 2898 9323</t>
+        </is>
+      </c>
+      <c r="P605" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q605" s="2" t="inlineStr">
+        <is>
+          <t>C0245344</t>
+        </is>
+      </c>
+      <c r="R605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kedington-wines-far-east-co-limited/</t>
+        </is>
+      </c>
+      <c r="S605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KedingtonWinesHongKong</t>
+        </is>
+      </c>
+      <c r="T605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kedingtonwineshk/</t>
+        </is>
+      </c>
+      <c r="U605" s="2" t="inlineStr"/>
+      <c r="V605" s="2" t="inlineStr"/>
+      <c r="W605" s="2" t="inlineStr">
+        <is>
+          <t>Max Yuen</t>
+        </is>
+      </c>
+      <c r="X605" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y605" s="2" t="inlineStr"/>
+      <c r="Z605" s="2" t="inlineStr"/>
+      <c r="AA605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-yuen-0aa169208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>Units F&amp;g, 18/f Golden Sun Centre  59-67 Bonham Strand West</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr"/>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>https://winepleasehk.com, https://www.kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="inlineStr"/>
+      <c r="K606" s="2" t="inlineStr"/>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M606" s="2" t="inlineStr"/>
+      <c r="N606" s="2" t="inlineStr">
+        <is>
+          <t>info@kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="O606" s="2" t="inlineStr">
+        <is>
+          <t>+852 2898 9323</t>
+        </is>
+      </c>
+      <c r="P606" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q606" s="2" t="inlineStr">
+        <is>
+          <t>C0245344</t>
+        </is>
+      </c>
+      <c r="R606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kedington-wines-far-east-co-limited/</t>
+        </is>
+      </c>
+      <c r="S606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KedingtonWinesHongKong</t>
+        </is>
+      </c>
+      <c r="T606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kedingtonwineshk/</t>
+        </is>
+      </c>
+      <c r="U606" s="2" t="inlineStr"/>
+      <c r="V606" s="2" t="inlineStr"/>
+      <c r="W606" s="2" t="inlineStr">
+        <is>
+          <t>Natalie Leung</t>
+        </is>
+      </c>
+      <c r="X606" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y606" s="2" t="inlineStr"/>
+      <c r="Z606" s="2" t="inlineStr"/>
+      <c r="AA606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/natalie-leung-a4503866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>122274</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>Jing Ho Industrial Building, 78-84 Wang Lung Street</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr"/>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>https://apus.us</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="inlineStr"/>
+      <c r="K607" s="2" t="inlineStr"/>
+      <c r="L607" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M607" s="2" t="inlineStr"/>
+      <c r="N607" s="2" t="inlineStr">
+        <is>
+          <t>info@apus.us</t>
+        </is>
+      </c>
+      <c r="O607" s="2" t="inlineStr">
+        <is>
+          <t>+852 3525 0550</t>
+        </is>
+      </c>
+      <c r="P607" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q607" s="2" t="inlineStr">
+        <is>
+          <t>14006171-000</t>
+        </is>
+      </c>
+      <c r="R607" s="2" t="inlineStr"/>
+      <c r="S607" s="2" t="inlineStr"/>
+      <c r="T607" s="2" t="inlineStr"/>
+      <c r="U607" s="2" t="inlineStr"/>
+      <c r="V607" s="2" t="inlineStr"/>
+      <c r="W607" s="2" t="inlineStr"/>
+      <c r="X607" s="2" t="inlineStr"/>
+      <c r="Y607" s="2" t="inlineStr"/>
+      <c r="Z607" s="2" t="inlineStr"/>
+      <c r="AA607" s="2" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>24981</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>317-319 Des Voeux Road Central</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr"/>
+      <c r="I608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="inlineStr"/>
+      <c r="K608" s="2" t="inlineStr"/>
+      <c r="L608" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M608" s="2" t="inlineStr"/>
+      <c r="N608" s="2" t="inlineStr">
+        <is>
+          <t>sales@asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="O608" s="2" t="inlineStr"/>
+      <c r="P608" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q608" s="2" t="inlineStr">
+        <is>
+          <t>74431249-000</t>
+        </is>
+      </c>
+      <c r="R608" s="2" t="inlineStr"/>
+      <c r="S608" s="2" t="inlineStr"/>
+      <c r="T608" s="2" t="inlineStr"/>
+      <c r="U608" s="2" t="inlineStr"/>
+      <c r="V608" s="2" t="inlineStr"/>
+      <c r="W608" s="2" t="inlineStr"/>
+      <c r="X608" s="2" t="inlineStr"/>
+      <c r="Y608" s="2" t="inlineStr"/>
+      <c r="Z608" s="2" t="inlineStr"/>
+      <c r="AA608" s="2" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>90923</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>Trans Asia Centre, 18 Kin Hong Street, Kwai Chung</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>1006-1007</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winpoasia.com</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="inlineStr"/>
+      <c r="K609" s="2" t="inlineStr"/>
+      <c r="L609" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M609" s="2" t="inlineStr"/>
+      <c r="N609" s="2" t="inlineStr">
+        <is>
+          <t>Info@winpoasia.com</t>
+        </is>
+      </c>
+      <c r="O609" s="2" t="inlineStr">
+        <is>
+          <t>+852 2423 8863</t>
+        </is>
+      </c>
+      <c r="P609" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q609" s="2" t="inlineStr">
+        <is>
+          <t>36759011-000</t>
+        </is>
+      </c>
+      <c r="R609" s="2" t="inlineStr"/>
+      <c r="S609" s="2" t="inlineStr"/>
+      <c r="T609" s="2" t="inlineStr"/>
+      <c r="U609" s="2" t="inlineStr"/>
+      <c r="V609" s="2" t="inlineStr"/>
+      <c r="W609" s="2" t="inlineStr"/>
+      <c r="X609" s="2" t="inlineStr"/>
+      <c r="Y609" s="2" t="inlineStr"/>
+      <c r="Z609" s="2" t="inlineStr"/>
+      <c r="AA609" s="2" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr"/>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="inlineStr"/>
+      <c r="K610" s="2" t="inlineStr"/>
+      <c r="L610" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M610" s="2" t="inlineStr"/>
+      <c r="N610" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O610" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P610" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q610" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R610" s="2" t="inlineStr"/>
+      <c r="S610" s="2" t="inlineStr"/>
+      <c r="T610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U610" s="2" t="inlineStr"/>
+      <c r="V610" s="2" t="inlineStr"/>
+      <c r="W610" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Cheung</t>
+        </is>
+      </c>
+      <c r="X610" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y610" s="2" t="inlineStr"/>
+      <c r="Z610" s="2" t="inlineStr"/>
+      <c r="AA610" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/ronald-cheung-44568278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr"/>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr"/>
+      <c r="K611" s="2" t="inlineStr"/>
+      <c r="L611" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M611" s="2" t="inlineStr"/>
+      <c r="N611" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O611" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P611" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q611" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R611" s="2" t="inlineStr"/>
+      <c r="S611" s="2" t="inlineStr"/>
+      <c r="T611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U611" s="2" t="inlineStr"/>
+      <c r="V611" s="2" t="inlineStr"/>
+      <c r="W611" s="2" t="inlineStr">
+        <is>
+          <t>Franky Hong</t>
+        </is>
+      </c>
+      <c r="X611" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y611" s="2" t="inlineStr"/>
+      <c r="Z611" s="2" t="inlineStr"/>
+      <c r="AA611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franky-hong-0a0a53aa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA611"/>
+  <dimension ref="A1:AA619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -62763,6 +62763,738 @@
         </is>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>Wine Guru Company Limited</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>Wine Guru Company Limited</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>117186</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>33-35 Yip Kan Street, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr"/>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineguru.com.hk, https://www.wineguruwines.com</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr"/>
+      <c r="K612" s="2" t="inlineStr"/>
+      <c r="L612" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M612" s="2" t="inlineStr"/>
+      <c r="N612" s="2" t="inlineStr">
+        <is>
+          <t>sales@wineguru.com.hk</t>
+        </is>
+      </c>
+      <c r="O612" s="2" t="inlineStr"/>
+      <c r="P612" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q612" s="2" t="inlineStr">
+        <is>
+          <t>60345218-000</t>
+        </is>
+      </c>
+      <c r="R612" s="2" t="inlineStr"/>
+      <c r="S612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineguruhk</t>
+        </is>
+      </c>
+      <c r="T612" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/wineguruhk</t>
+        </is>
+      </c>
+      <c r="U612" s="2" t="inlineStr"/>
+      <c r="V612" s="2" t="inlineStr"/>
+      <c r="W612" s="2" t="inlineStr"/>
+      <c r="X612" s="2" t="inlineStr"/>
+      <c r="Y612" s="2" t="inlineStr"/>
+      <c r="Z612" s="2" t="inlineStr"/>
+      <c r="AA612" s="2" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>Units F&amp;g, 18/f Golden Sun Centre  59-67 Bonham Strand West</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr"/>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>https://winepleasehk.com, https://www.kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="inlineStr"/>
+      <c r="K613" s="2" t="inlineStr"/>
+      <c r="L613" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M613" s="2" t="inlineStr"/>
+      <c r="N613" s="2" t="inlineStr">
+        <is>
+          <t>info@kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="O613" s="2" t="inlineStr">
+        <is>
+          <t>+852 2898 9323</t>
+        </is>
+      </c>
+      <c r="P613" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q613" s="2" t="inlineStr">
+        <is>
+          <t>C0245344</t>
+        </is>
+      </c>
+      <c r="R613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kedington-wines-far-east-co-limited/</t>
+        </is>
+      </c>
+      <c r="S613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KedingtonWinesHongKong</t>
+        </is>
+      </c>
+      <c r="T613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kedingtonwineshk/</t>
+        </is>
+      </c>
+      <c r="U613" s="2" t="inlineStr"/>
+      <c r="V613" s="2" t="inlineStr"/>
+      <c r="W613" s="2" t="inlineStr">
+        <is>
+          <t>Max Yuen</t>
+        </is>
+      </c>
+      <c r="X613" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y613" s="2" t="inlineStr"/>
+      <c r="Z613" s="2" t="inlineStr"/>
+      <c r="AA613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-yuen-0aa169208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>Units F&amp;g, 18/f Golden Sun Centre  59-67 Bonham Strand West</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr"/>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>https://winepleasehk.com, https://www.kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="inlineStr"/>
+      <c r="K614" s="2" t="inlineStr"/>
+      <c r="L614" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M614" s="2" t="inlineStr"/>
+      <c r="N614" s="2" t="inlineStr">
+        <is>
+          <t>info@kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="O614" s="2" t="inlineStr">
+        <is>
+          <t>+852 2898 9323</t>
+        </is>
+      </c>
+      <c r="P614" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q614" s="2" t="inlineStr">
+        <is>
+          <t>C0245344</t>
+        </is>
+      </c>
+      <c r="R614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kedington-wines-far-east-co-limited/</t>
+        </is>
+      </c>
+      <c r="S614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KedingtonWinesHongKong</t>
+        </is>
+      </c>
+      <c r="T614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kedingtonwineshk/</t>
+        </is>
+      </c>
+      <c r="U614" s="2" t="inlineStr"/>
+      <c r="V614" s="2" t="inlineStr"/>
+      <c r="W614" s="2" t="inlineStr">
+        <is>
+          <t>Natalie Leung</t>
+        </is>
+      </c>
+      <c r="X614" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y614" s="2" t="inlineStr"/>
+      <c r="Z614" s="2" t="inlineStr"/>
+      <c r="AA614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/natalie-leung-a4503866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>122274</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>Jing Ho Industrial Building, 78-84 Wang Lung Street</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr"/>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>https://apus.us</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="inlineStr"/>
+      <c r="K615" s="2" t="inlineStr"/>
+      <c r="L615" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M615" s="2" t="inlineStr"/>
+      <c r="N615" s="2" t="inlineStr">
+        <is>
+          <t>info@apus.us</t>
+        </is>
+      </c>
+      <c r="O615" s="2" t="inlineStr">
+        <is>
+          <t>+852 3525 0550</t>
+        </is>
+      </c>
+      <c r="P615" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q615" s="2" t="inlineStr">
+        <is>
+          <t>14006171-000</t>
+        </is>
+      </c>
+      <c r="R615" s="2" t="inlineStr"/>
+      <c r="S615" s="2" t="inlineStr"/>
+      <c r="T615" s="2" t="inlineStr"/>
+      <c r="U615" s="2" t="inlineStr"/>
+      <c r="V615" s="2" t="inlineStr"/>
+      <c r="W615" s="2" t="inlineStr"/>
+      <c r="X615" s="2" t="inlineStr"/>
+      <c r="Y615" s="2" t="inlineStr"/>
+      <c r="Z615" s="2" t="inlineStr"/>
+      <c r="AA615" s="2" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>24981</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>317-319 Des Voeux Road Central</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr"/>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr"/>
+      <c r="K616" s="2" t="inlineStr"/>
+      <c r="L616" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M616" s="2" t="inlineStr"/>
+      <c r="N616" s="2" t="inlineStr">
+        <is>
+          <t>sales@asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="O616" s="2" t="inlineStr"/>
+      <c r="P616" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q616" s="2" t="inlineStr">
+        <is>
+          <t>74431249-000</t>
+        </is>
+      </c>
+      <c r="R616" s="2" t="inlineStr"/>
+      <c r="S616" s="2" t="inlineStr"/>
+      <c r="T616" s="2" t="inlineStr"/>
+      <c r="U616" s="2" t="inlineStr"/>
+      <c r="V616" s="2" t="inlineStr"/>
+      <c r="W616" s="2" t="inlineStr"/>
+      <c r="X616" s="2" t="inlineStr"/>
+      <c r="Y616" s="2" t="inlineStr"/>
+      <c r="Z616" s="2" t="inlineStr"/>
+      <c r="AA616" s="2" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>90923</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>Trans Asia Centre, 18 Kin Hong Street, Kwai Chung</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>1006-1007</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winpoasia.com</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="inlineStr"/>
+      <c r="K617" s="2" t="inlineStr"/>
+      <c r="L617" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M617" s="2" t="inlineStr"/>
+      <c r="N617" s="2" t="inlineStr">
+        <is>
+          <t>Info@winpoasia.com</t>
+        </is>
+      </c>
+      <c r="O617" s="2" t="inlineStr">
+        <is>
+          <t>+852 2423 8863</t>
+        </is>
+      </c>
+      <c r="P617" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q617" s="2" t="inlineStr">
+        <is>
+          <t>36759011-000</t>
+        </is>
+      </c>
+      <c r="R617" s="2" t="inlineStr"/>
+      <c r="S617" s="2" t="inlineStr"/>
+      <c r="T617" s="2" t="inlineStr"/>
+      <c r="U617" s="2" t="inlineStr"/>
+      <c r="V617" s="2" t="inlineStr"/>
+      <c r="W617" s="2" t="inlineStr"/>
+      <c r="X617" s="2" t="inlineStr"/>
+      <c r="Y617" s="2" t="inlineStr"/>
+      <c r="Z617" s="2" t="inlineStr"/>
+      <c r="AA617" s="2" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr"/>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr"/>
+      <c r="K618" s="2" t="inlineStr"/>
+      <c r="L618" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M618" s="2" t="inlineStr"/>
+      <c r="N618" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O618" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P618" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q618" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R618" s="2" t="inlineStr"/>
+      <c r="S618" s="2" t="inlineStr"/>
+      <c r="T618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U618" s="2" t="inlineStr"/>
+      <c r="V618" s="2" t="inlineStr"/>
+      <c r="W618" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Cheung</t>
+        </is>
+      </c>
+      <c r="X618" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y618" s="2" t="inlineStr"/>
+      <c r="Z618" s="2" t="inlineStr"/>
+      <c r="AA618" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/ronald-cheung-44568278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr"/>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="inlineStr"/>
+      <c r="K619" s="2" t="inlineStr"/>
+      <c r="L619" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M619" s="2" t="inlineStr"/>
+      <c r="N619" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O619" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P619" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q619" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R619" s="2" t="inlineStr"/>
+      <c r="S619" s="2" t="inlineStr"/>
+      <c r="T619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U619" s="2" t="inlineStr"/>
+      <c r="V619" s="2" t="inlineStr"/>
+      <c r="W619" s="2" t="inlineStr">
+        <is>
+          <t>Franky Hong</t>
+        </is>
+      </c>
+      <c r="X619" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y619" s="2" t="inlineStr"/>
+      <c r="Z619" s="2" t="inlineStr"/>
+      <c r="AA619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franky-hong-0a0a53aa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA619"/>
+  <dimension ref="A1:AA627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -63495,6 +63495,738 @@
         </is>
       </c>
     </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>Wine Guru Company Limited</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>Wine Guru Company Limited</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>117186</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>33-35 Yip Kan Street, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr"/>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineguru.com.hk, https://www.wineguruwines.com</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="inlineStr"/>
+      <c r="K620" s="2" t="inlineStr"/>
+      <c r="L620" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M620" s="2" t="inlineStr"/>
+      <c r="N620" s="2" t="inlineStr">
+        <is>
+          <t>sales@wineguru.com.hk</t>
+        </is>
+      </c>
+      <c r="O620" s="2" t="inlineStr"/>
+      <c r="P620" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q620" s="2" t="inlineStr">
+        <is>
+          <t>60345218-000</t>
+        </is>
+      </c>
+      <c r="R620" s="2" t="inlineStr"/>
+      <c r="S620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineguruhk</t>
+        </is>
+      </c>
+      <c r="T620" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/wineguruhk</t>
+        </is>
+      </c>
+      <c r="U620" s="2" t="inlineStr"/>
+      <c r="V620" s="2" t="inlineStr"/>
+      <c r="W620" s="2" t="inlineStr"/>
+      <c r="X620" s="2" t="inlineStr"/>
+      <c r="Y620" s="2" t="inlineStr"/>
+      <c r="Z620" s="2" t="inlineStr"/>
+      <c r="AA620" s="2" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>Units F&amp;g, 18/f Golden Sun Centre  59-67 Bonham Strand West</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr"/>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>https://winepleasehk.com, https://www.kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="inlineStr"/>
+      <c r="K621" s="2" t="inlineStr"/>
+      <c r="L621" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M621" s="2" t="inlineStr"/>
+      <c r="N621" s="2" t="inlineStr">
+        <is>
+          <t>info@kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="O621" s="2" t="inlineStr">
+        <is>
+          <t>+852 2898 9323</t>
+        </is>
+      </c>
+      <c r="P621" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q621" s="2" t="inlineStr">
+        <is>
+          <t>C0245344</t>
+        </is>
+      </c>
+      <c r="R621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kedington-wines-far-east-co-limited/</t>
+        </is>
+      </c>
+      <c r="S621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KedingtonWinesHongKong</t>
+        </is>
+      </c>
+      <c r="T621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kedingtonwineshk/</t>
+        </is>
+      </c>
+      <c r="U621" s="2" t="inlineStr"/>
+      <c r="V621" s="2" t="inlineStr"/>
+      <c r="W621" s="2" t="inlineStr">
+        <is>
+          <t>Max Yuen</t>
+        </is>
+      </c>
+      <c r="X621" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y621" s="2" t="inlineStr"/>
+      <c r="Z621" s="2" t="inlineStr"/>
+      <c r="AA621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-yuen-0aa169208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>Kedington Wines (far East) Co Limited</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>Units F&amp;g, 18/f Golden Sun Centre  59-67 Bonham Strand West</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr"/>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>https://winepleasehk.com, https://www.kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="inlineStr"/>
+      <c r="K622" s="2" t="inlineStr"/>
+      <c r="L622" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M622" s="2" t="inlineStr"/>
+      <c r="N622" s="2" t="inlineStr">
+        <is>
+          <t>info@kedingtonwines.com</t>
+        </is>
+      </c>
+      <c r="O622" s="2" t="inlineStr">
+        <is>
+          <t>+852 2898 9323</t>
+        </is>
+      </c>
+      <c r="P622" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q622" s="2" t="inlineStr">
+        <is>
+          <t>C0245344</t>
+        </is>
+      </c>
+      <c r="R622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kedington-wines-far-east-co-limited/</t>
+        </is>
+      </c>
+      <c r="S622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KedingtonWinesHongKong</t>
+        </is>
+      </c>
+      <c r="T622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kedingtonwineshk/</t>
+        </is>
+      </c>
+      <c r="U622" s="2" t="inlineStr"/>
+      <c r="V622" s="2" t="inlineStr"/>
+      <c r="W622" s="2" t="inlineStr">
+        <is>
+          <t>Natalie Leung</t>
+        </is>
+      </c>
+      <c r="X622" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y622" s="2" t="inlineStr"/>
+      <c r="Z622" s="2" t="inlineStr"/>
+      <c r="AA622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/natalie-leung-a4503866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>Apus Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>122274</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>Jing Ho Industrial Building, 78-84 Wang Lung Street</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr"/>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>https://apus.us</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="inlineStr"/>
+      <c r="K623" s="2" t="inlineStr"/>
+      <c r="L623" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M623" s="2" t="inlineStr"/>
+      <c r="N623" s="2" t="inlineStr">
+        <is>
+          <t>info@apus.us</t>
+        </is>
+      </c>
+      <c r="O623" s="2" t="inlineStr">
+        <is>
+          <t>+852 3525 0550</t>
+        </is>
+      </c>
+      <c r="P623" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q623" s="2" t="inlineStr">
+        <is>
+          <t>14006171-000</t>
+        </is>
+      </c>
+      <c r="R623" s="2" t="inlineStr"/>
+      <c r="S623" s="2" t="inlineStr"/>
+      <c r="T623" s="2" t="inlineStr"/>
+      <c r="U623" s="2" t="inlineStr"/>
+      <c r="V623" s="2" t="inlineStr"/>
+      <c r="W623" s="2" t="inlineStr"/>
+      <c r="X623" s="2" t="inlineStr"/>
+      <c r="Y623" s="2" t="inlineStr"/>
+      <c r="Z623" s="2" t="inlineStr"/>
+      <c r="AA623" s="2" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>Asia Pacific (international) Management Limited</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>24981</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>317-319 Des Voeux Road Central</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr"/>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="J624" s="2" t="inlineStr"/>
+      <c r="K624" s="2" t="inlineStr"/>
+      <c r="L624" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M624" s="2" t="inlineStr"/>
+      <c r="N624" s="2" t="inlineStr">
+        <is>
+          <t>sales@asiapacific-intl.com</t>
+        </is>
+      </c>
+      <c r="O624" s="2" t="inlineStr"/>
+      <c r="P624" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q624" s="2" t="inlineStr">
+        <is>
+          <t>74431249-000</t>
+        </is>
+      </c>
+      <c r="R624" s="2" t="inlineStr"/>
+      <c r="S624" s="2" t="inlineStr"/>
+      <c r="T624" s="2" t="inlineStr"/>
+      <c r="U624" s="2" t="inlineStr"/>
+      <c r="V624" s="2" t="inlineStr"/>
+      <c r="W624" s="2" t="inlineStr"/>
+      <c r="X624" s="2" t="inlineStr"/>
+      <c r="Y624" s="2" t="inlineStr"/>
+      <c r="Z624" s="2" t="inlineStr"/>
+      <c r="AA624" s="2" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>Winpo Asia Limited</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>90923</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>Trans Asia Centre, 18 Kin Hong Street, Kwai Chung</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>1006-1007</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winpoasia.com</t>
+        </is>
+      </c>
+      <c r="J625" s="2" t="inlineStr"/>
+      <c r="K625" s="2" t="inlineStr"/>
+      <c r="L625" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M625" s="2" t="inlineStr"/>
+      <c r="N625" s="2" t="inlineStr">
+        <is>
+          <t>Info@winpoasia.com</t>
+        </is>
+      </c>
+      <c r="O625" s="2" t="inlineStr">
+        <is>
+          <t>+852 2423 8863</t>
+        </is>
+      </c>
+      <c r="P625" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q625" s="2" t="inlineStr">
+        <is>
+          <t>36759011-000</t>
+        </is>
+      </c>
+      <c r="R625" s="2" t="inlineStr"/>
+      <c r="S625" s="2" t="inlineStr"/>
+      <c r="T625" s="2" t="inlineStr"/>
+      <c r="U625" s="2" t="inlineStr"/>
+      <c r="V625" s="2" t="inlineStr"/>
+      <c r="W625" s="2" t="inlineStr"/>
+      <c r="X625" s="2" t="inlineStr"/>
+      <c r="Y625" s="2" t="inlineStr"/>
+      <c r="Z625" s="2" t="inlineStr"/>
+      <c r="AA625" s="2" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr"/>
+      <c r="I626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J626" s="2" t="inlineStr"/>
+      <c r="K626" s="2" t="inlineStr"/>
+      <c r="L626" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M626" s="2" t="inlineStr"/>
+      <c r="N626" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O626" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P626" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q626" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R626" s="2" t="inlineStr"/>
+      <c r="S626" s="2" t="inlineStr"/>
+      <c r="T626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U626" s="2" t="inlineStr"/>
+      <c r="V626" s="2" t="inlineStr"/>
+      <c r="W626" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Cheung</t>
+        </is>
+      </c>
+      <c r="X626" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y626" s="2" t="inlineStr"/>
+      <c r="Z626" s="2" t="inlineStr"/>
+      <c r="AA626" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/ronald-cheung-44568278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>Tandron Spirits International Limited</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>8 Luk Hop Street, San Po Kong</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr"/>
+      <c r="I627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="J627" s="2" t="inlineStr"/>
+      <c r="K627" s="2" t="inlineStr"/>
+      <c r="L627" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M627" s="2" t="inlineStr"/>
+      <c r="N627" s="2" t="inlineStr">
+        <is>
+          <t>info@tandron.com.hk</t>
+        </is>
+      </c>
+      <c r="O627" s="2" t="inlineStr">
+        <is>
+          <t>+852 2668 5072</t>
+        </is>
+      </c>
+      <c r="P627" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q627" s="2" t="inlineStr">
+        <is>
+          <t>60233423-000</t>
+        </is>
+      </c>
+      <c r="R627" s="2" t="inlineStr"/>
+      <c r="S627" s="2" t="inlineStr"/>
+      <c r="T627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakutsuruhk</t>
+        </is>
+      </c>
+      <c r="U627" s="2" t="inlineStr"/>
+      <c r="V627" s="2" t="inlineStr"/>
+      <c r="W627" s="2" t="inlineStr">
+        <is>
+          <t>Franky Hong</t>
+        </is>
+      </c>
+      <c r="X627" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y627" s="2" t="inlineStr"/>
+      <c r="Z627" s="2" t="inlineStr"/>
+      <c r="AA627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franky-hong-0a0a53aa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
